--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Gilt Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Gilt Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="87">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Gilt Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -73,24 +73,51 @@
     <t>IN0020200120</t>
   </si>
   <si>
-    <t>IN0020230085</t>
+    <t>IN0020240035</t>
+  </si>
+  <si>
+    <t>IN0020240126</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>IN0020250018</t>
+  </si>
+  <si>
+    <t>State Government of Chhattisgarh</t>
+  </si>
+  <si>
+    <t>IN3520240083</t>
   </si>
   <si>
     <t>IN0020210137</t>
   </si>
   <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>IN0020240142</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
+  </si>
+  <si>
     <t>IN0020240134</t>
   </si>
   <si>
-    <t>IN0020240126</t>
-  </si>
-  <si>
-    <t>State Government of Rajasthan</t>
-  </si>
-  <si>
-    <t>IN2920140240</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
@@ -130,40 +157,25 @@
     <t>Treasury Bills</t>
   </si>
   <si>
+    <t>182 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Y399</t>
+  </si>
+  <si>
+    <t>IN002024Y415</t>
+  </si>
+  <si>
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X375</t>
-  </si>
-  <si>
-    <t>IN002024X417</t>
+    <t>IN002024X490</t>
   </si>
   <si>
     <t>364 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002023Z471</t>
-  </si>
-  <si>
-    <t>IN002024X326</t>
-  </si>
-  <si>
-    <t>IN002024X425</t>
-  </si>
-  <si>
-    <t>IN002024X342</t>
-  </si>
-  <si>
-    <t>182 Days Treasury Bills</t>
-  </si>
-  <si>
-    <t>IN002024Y191</t>
-  </si>
-  <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>Reverse Repo</t>
+    <t>IN002024Z149</t>
   </si>
   <si>
     <t>Units of an Alternative Investment Fund (AIF)</t>
@@ -178,6 +190,66 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEREST RATE SWAPS (At Notional Value) </t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> DBS Bank India Ltd- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t>GSCCIL- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Nomura Fixed Income Securities Ltd- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -15-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -22-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> ICICI Securities Primary Dealership Ltd.- MD -17-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -187,7 +259,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -202,7 +274,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - NIFTY All Duration G-Sec Index</t>
+    <t>Benchmark name - CRISIL Dynamic Gilt Index</t>
   </si>
 </sst>
 </file>
@@ -290,7 +362,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -376,6 +448,14 @@
         <color auto="1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -402,7 +482,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -480,6 +560,9 @@
       <protection/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -580,13 +663,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -604,8 +687,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="14249400"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="20564475"/>
+          <a:ext cx="6381750" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -619,13 +702,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -643,8 +726,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="17106900"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="23421975"/>
+          <a:ext cx="6381750" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -977,19 +1060,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J84"/>
+  <dimension ref="B1:J117"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="16.142857142857142" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="19.714285714285715" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="12.571428571428571" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="23" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="23" width="95.71428571428571" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="23" width="16.142857142857142" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="23" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="23" width="19.714285714285715" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="23" width="12.285714285714286" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="23" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="23" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="23" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="23" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1077,10 +1160,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>373644.36</v>
+        <v>515988.76</v>
       </c>
       <c r="H5" s="10">
-        <v>0.5874178231695</v>
+        <v>0.7023108437066999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1114,10 +1197,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>373644.36</v>
+        <v>515988.76</v>
       </c>
       <c r="H7" s="10">
-        <v>0.5874178231695</v>
+        <v>0.7023108437066999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1151,10 +1234,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>373644.36</v>
+        <v>515988.76</v>
       </c>
       <c r="H9" s="10">
-        <v>0.5874178231695</v>
+        <v>0.7023108437066999</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1177,16 +1260,16 @@
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>251066000</v>
+        <v>170285400</v>
       </c>
       <c r="G10" s="16">
-        <v>257107.65</v>
+        <v>179511.46</v>
       </c>
       <c r="H10" s="17">
-        <v>0.4042068668809</v>
+        <v>0.2443325411345</v>
       </c>
       <c r="I10" s="16">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1200,7 +1283,7 @@
         <v>18</v>
       </c>
       <c r="D11" s="14">
-        <v>7.930000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
@@ -1209,13 +1292,13 @@
         <v>94096700</v>
       </c>
       <c r="G11" s="16">
-        <v>96507.08</v>
+        <v>97713.97</v>
       </c>
       <c r="H11" s="17">
-        <v>0.1517217571652</v>
+        <v>0.1329982085514</v>
       </c>
       <c r="I11" s="16">
-        <v>7.66</v>
+        <v>7.31</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1229,22 +1312,22 @@
         <v>19</v>
       </c>
       <c r="D12" s="14">
-        <v>7.18</v>
+        <v>7.34</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="15">
-        <v>10830390</v>
+        <v>79038200</v>
       </c>
       <c r="G12" s="16">
-        <v>11126.55</v>
+        <v>84130.95</v>
       </c>
       <c r="H12" s="17">
-        <v>0.017492392446</v>
+        <v>0.1145103983977</v>
       </c>
       <c r="I12" s="16">
-        <v>6.87</v>
+        <v>6.98</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1258,22 +1341,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>7.53</v>
+        <v>6.79</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="15">
-        <v>7500000</v>
+        <v>64485590</v>
       </c>
       <c r="G13" s="16">
-        <v>7554.65</v>
+        <v>66802.49</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0118768982831</v>
+        <v>0.09092468044</v>
       </c>
       <c r="I13" s="16">
-        <v>7.47</v>
+        <v>6.37</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>13</v>
@@ -1281,28 +1364,28 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="14">
-        <v>6.92</v>
+        <v>7.12</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="15">
-        <v>845400</v>
+        <v>21496400</v>
       </c>
       <c r="G14" s="16">
-        <v>852.85</v>
+        <v>22219.52</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0013407917905</v>
+        <v>0.0302429259078</v>
       </c>
       <c r="I14" s="16">
-        <v>6.94</v>
+        <v>6.83</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1310,28 +1393,28 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="14">
-        <v>6.79</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="15">
-        <v>436650</v>
+        <v>18000000</v>
       </c>
       <c r="G15" s="16">
-        <v>439.53</v>
+        <v>18679.59</v>
       </c>
       <c r="H15" s="17">
-        <v>0.00069099867</v>
+        <v>0.0254247371842</v>
       </c>
       <c r="I15" s="16">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
@@ -1339,28 +1422,28 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="14">
-        <v>8.05</v>
+        <v>6.90</v>
       </c>
       <c r="E16" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="15">
-        <v>56000</v>
+        <v>15000000</v>
       </c>
       <c r="G16" s="16">
-        <v>56.05</v>
+        <v>15100.98</v>
       </c>
       <c r="H16" s="17">
-        <v>0.0000881179338</v>
+        <v>0.0205539012218</v>
       </c>
       <c r="I16" s="16">
-        <v>6.67</v>
+        <v>6.97</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1368,36 +1451,57 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>13</v>
+        <v>25</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="14">
+        <v>7.32</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="15">
+        <v>8288200</v>
+      </c>
+      <c r="G17" s="16">
+        <v>8699.52</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0.0118408920982</v>
+      </c>
+      <c r="I17" s="16">
+        <v>6.81</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
-      <c r="B18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>13</v>
+      <c r="B18" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="14">
+        <v>6.99</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="15">
+        <v>7500000</v>
+      </c>
+      <c r="G18" s="16">
+        <v>7655.73</v>
+      </c>
+      <c r="H18" s="17">
+        <v>0.0104201924776</v>
+      </c>
+      <c r="I18" s="16">
+        <v>6.80</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1405,36 +1509,57 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="14">
+        <v>7.13</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="15">
+        <v>7321700</v>
+      </c>
+      <c r="G19" s="16">
+        <v>7562.95</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0.0102939098817</v>
+      </c>
+      <c r="I19" s="16">
+        <v>6.75</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
-      <c r="B20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>13</v>
+      <c r="B20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>7.09</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="15">
+        <v>5000000</v>
+      </c>
+      <c r="G20" s="16">
+        <v>5150.54</v>
+      </c>
+      <c r="H20" s="17">
+        <v>0.0070103854451</v>
+      </c>
+      <c r="I20" s="16">
+        <v>6.99</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
@@ -1442,36 +1567,57 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>13</v>
+        <v>31</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="14">
+        <v>7.29</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="15">
+        <v>2599500</v>
+      </c>
+      <c r="G21" s="16">
+        <v>2713.52</v>
+      </c>
+      <c r="H21" s="17">
+        <v>0.003693364407</v>
+      </c>
+      <c r="I21" s="16">
+        <v>6.88</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
-      <c r="B22" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>13</v>
+      <c r="B22" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="14">
+        <v>6.92</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="15">
+        <v>45400</v>
+      </c>
+      <c r="G22" s="16">
+        <v>47.54</v>
+      </c>
+      <c r="H22" s="17">
+        <v>0.0000647065597</v>
+      </c>
+      <c r="I22" s="16">
+        <v>6.52</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -1487,7 +1633,7 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>13</v>
@@ -1502,10 +1648,10 @@
         <v>13</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>13</v>
@@ -1524,7 +1670,7 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>13</v>
@@ -1539,10 +1685,10 @@
         <v>13</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>13</v>
@@ -1561,7 +1707,7 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>13</v>
@@ -1576,10 +1722,10 @@
         <v>13</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>13</v>
@@ -1598,7 +1744,7 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>13</v>
@@ -1613,10 +1759,10 @@
         <v>13</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>13</v>
@@ -1635,7 +1781,7 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>13</v>
@@ -1649,11 +1795,11 @@
       <c r="F32" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="9">
-        <v>147880.95</v>
-      </c>
-      <c r="H32" s="10">
-        <v>0.2324882027852</v>
+      <c r="G32" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>13</v>
@@ -1672,7 +1818,7 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>13</v>
@@ -1687,10 +1833,10 @@
         <v>13</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>13</v>
@@ -1709,25 +1855,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="H36" s="10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>13</v>
@@ -1746,7 +1892,7 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>13</v>
@@ -1760,11 +1906,11 @@
       <c r="F38" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>26</v>
+      <c r="G38" s="9">
+        <v>76548.99</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0.1041906140586</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>13</v>
@@ -1783,7 +1929,7 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>13</v>
@@ -1797,11 +1943,11 @@
       <c r="F40" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G40" s="9">
-        <v>147880.95</v>
-      </c>
-      <c r="H40" s="10">
-        <v>0.2324882027852</v>
+      <c r="G40" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>13</v>
@@ -1812,57 +1958,36 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="15">
-        <v>35000000</v>
-      </c>
-      <c r="G41" s="16">
-        <v>34712.83</v>
-      </c>
-      <c r="H41" s="17">
-        <v>0.0545731107373</v>
-      </c>
-      <c r="I41" s="16">
-        <v>6.43</v>
+        <v>13</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
-      <c r="B42" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="15">
-        <v>27500000</v>
-      </c>
-      <c r="G42" s="16">
-        <v>27136.59</v>
-      </c>
-      <c r="H42" s="17">
-        <v>0.0426622701492</v>
-      </c>
-      <c r="I42" s="16">
-        <v>6.52</v>
+      <c r="B42" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -1870,57 +1995,36 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" s="15">
-        <v>22500000</v>
-      </c>
-      <c r="G43" s="16">
-        <v>22480.40</v>
-      </c>
-      <c r="H43" s="17">
-        <v>0.0353421302331</v>
-      </c>
-      <c r="I43" s="16">
-        <v>6.37</v>
+        <v>13</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
-      <c r="B44" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="15">
-        <v>20000000</v>
-      </c>
-      <c r="G44" s="16">
-        <v>19957.86</v>
-      </c>
-      <c r="H44" s="17">
-        <v>0.031376367293</v>
-      </c>
-      <c r="I44" s="16">
-        <v>6.42</v>
+      <c r="B44" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -1928,57 +2032,36 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" s="15">
-        <v>19000000</v>
-      </c>
-      <c r="G45" s="16">
-        <v>18725.98</v>
-      </c>
-      <c r="H45" s="17">
-        <v>0.0294396907485</v>
-      </c>
-      <c r="I45" s="16">
-        <v>6.51</v>
+        <v>13</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
-      <c r="B46" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="15">
-        <v>15000000</v>
-      </c>
-      <c r="G46" s="16">
-        <v>14931.66</v>
-      </c>
-      <c r="H46" s="17">
-        <v>0.0234745232432</v>
-      </c>
-      <c r="I46" s="16">
-        <v>6.43</v>
+      <c r="B46" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="9">
+        <v>76548.99</v>
+      </c>
+      <c r="H46" s="10">
+        <v>0.1041906140586</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -1986,10 +2069,10 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
@@ -1998,16 +2081,16 @@
         <v>17</v>
       </c>
       <c r="F47" s="15">
-        <v>5000000</v>
+        <v>40000000</v>
       </c>
       <c r="G47" s="16">
-        <v>4995.65</v>
+        <v>39762.16</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0078538154525</v>
+        <v>0.0541201636586</v>
       </c>
       <c r="I47" s="16">
-        <v>6.37</v>
+        <v>5.60</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2015,10 +2098,10 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
@@ -2027,16 +2110,16 @@
         <v>17</v>
       </c>
       <c r="F48" s="15">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="G48" s="16">
-        <v>4939.98</v>
+        <v>19838.32</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0077662949284</v>
+        <v>0.0270018813141</v>
       </c>
       <c r="I48" s="16">
-        <v>6.52</v>
+        <v>5.61</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2044,36 +2127,57 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>13</v>
+        <v>50</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="15">
+        <v>10000000</v>
+      </c>
+      <c r="G49" s="16">
+        <v>9982.85</v>
+      </c>
+      <c r="H49" s="17">
+        <v>0.0135876289361</v>
+      </c>
+      <c r="I49" s="16">
+        <v>5.70</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
-      <c r="B50" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="9">
-        <v>74189.93</v>
-      </c>
-      <c r="H50" s="10">
-        <v>0.1166362772924</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>13</v>
+      <c r="B50" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="15">
+        <v>7000000</v>
+      </c>
+      <c r="G50" s="16">
+        <v>6965.66</v>
+      </c>
+      <c r="H50" s="17">
+        <v>0.0094809401498</v>
+      </c>
+      <c r="I50" s="16">
+        <v>5.62</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2089,7 +2193,7 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>13</v>
@@ -2104,10 +2208,10 @@
         <v>13</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>13</v>
@@ -2126,7 +2230,7 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>13</v>
@@ -2141,10 +2245,10 @@
         <v>13</v>
       </c>
       <c r="G54" s="9">
-        <v>31168.49</v>
+        <v>138244.7</v>
       </c>
       <c r="H54" s="10">
-        <v>0.0490009445005</v>
+        <v>0.188164470666</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>13</v>
@@ -2163,7 +2267,7 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>13</v>
@@ -2178,10 +2282,10 @@
         <v>13</v>
       </c>
       <c r="G56" s="19">
-        <v>9195.64189184003</v>
+        <v>3918.9498479700414</v>
       </c>
       <c r="H56" s="20">
-        <v>0.014456752251672882</v>
+        <v>0.00533407156809689</v>
       </c>
       <c r="I56" s="19" t="s">
         <v>13</v>
@@ -2192,7 +2296,7 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="18" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>13</v>
@@ -2207,10 +2311,10 @@
         <v>13</v>
       </c>
       <c r="G57" s="19">
-        <v>636079.37189184</v>
+        <v>734701.39984797</v>
       </c>
       <c r="H57" s="20">
-        <v>0.9999999999992728</v>
+        <v>0.9999999999993968</v>
       </c>
       <c r="I57" s="19" t="s">
         <v>13</v>
@@ -2219,98 +2323,1055 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="2:9" ht="15" customHeight="1">
-      <c r="B60" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
-    </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
-      <c r="B61" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-    </row>
-    <row r="62" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B62" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-    </row>
-    <row r="63" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B63" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-    </row>
-    <row r="64" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B64" s="23" t="s">
+    <row r="58" spans="2:10" ht="15" customHeight="1">
+      <c r="B58" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" ht="15" customHeight="1">
+      <c r="B59" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="22"/>
-    </row>
-    <row r="65" spans="2:7" ht="51" customHeight="1">
-      <c r="B65" s="24" t="s">
+      <c r="C59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="19">
+        <v>-240000</v>
+      </c>
+      <c r="H59" s="20">
+        <v>-0.3266633220648045</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" ht="15" customHeight="1">
+      <c r="B60" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-    </row>
-    <row r="68" ht="15">
-      <c r="B68" s="22" t="s">
+      <c r="C60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H60" s="17">
+        <v>-0.010208228814525135</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" ht="15" customHeight="1">
+      <c r="B61" s="12" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="83" ht="15">
-      <c r="B83" s="22" t="s">
+      <c r="C61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H61" s="17">
+        <v>-0.006805485876350091</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" ht="15" customHeight="1">
+      <c r="B62" s="12" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="84" ht="15">
-      <c r="B84" s="22" t="s">
+      <c r="C62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H62" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" ht="15" customHeight="1">
+      <c r="B63" s="12" t="s">
         <v>62</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H63" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" ht="15" customHeight="1">
+      <c r="B64" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G64" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H64" s="17">
+        <v>-0.010208228814525135</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" ht="15" customHeight="1">
+      <c r="B65" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H65" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="15" customHeight="1">
+      <c r="B66" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H66" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" ht="15" customHeight="1">
+      <c r="B67" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H67" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" ht="15" customHeight="1">
+      <c r="B68" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H68" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" ht="15" customHeight="1">
+      <c r="B69" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G69" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H69" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J69" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="15" customHeight="1">
+      <c r="B70" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G70" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H70" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" ht="15" customHeight="1">
+      <c r="B71" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H71" s="17">
+        <v>-0.006805485876350091</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1">
+      <c r="B72" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H72" s="17">
+        <v>-0.006805485876350091</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15" customHeight="1">
+      <c r="B73" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H73" s="17">
+        <v>-0.010208228814525135</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1">
+      <c r="B74" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H74" s="17">
+        <v>-0.010208228814525135</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1">
+      <c r="B75" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H75" s="17">
+        <v>-0.006805485876350091</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1">
+      <c r="B76" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H76" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1">
+      <c r="B77" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G77" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H77" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1">
+      <c r="B78" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H78" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1">
+      <c r="B79" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G79" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H79" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1">
+      <c r="B80" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H80" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G81" s="16">
+        <v>-2500</v>
+      </c>
+      <c r="H81" s="17">
+        <v>-0.0034027429381750453</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1">
+      <c r="B82" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="16">
+        <v>-7500</v>
+      </c>
+      <c r="H82" s="17">
+        <v>-0.010208228814525135</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1">
+      <c r="B83" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H83" s="17">
+        <v>-0.006805485876350091</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H84" s="17">
+        <v>-0.006805485876350091</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1">
+      <c r="B85" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H85" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H86" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1">
+      <c r="B87" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H87" s="17">
+        <v>-0.006805485876350091</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="15" customHeight="1">
+      <c r="B88" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="16">
+        <v>-10000</v>
+      </c>
+      <c r="H88" s="17">
+        <v>-0.013610971752700181</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H89" s="17">
+        <v>-0.006805485876350091</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15" customHeight="1">
+      <c r="B90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="15" customHeight="1">
+      <c r="B93" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C93" s="23"/>
+      <c r="D93" s="23"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="23"/>
+    </row>
+    <row r="94" spans="2:8" ht="15" customHeight="1">
+      <c r="B94" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="23"/>
+      <c r="D94" s="23"/>
+      <c r="E94" s="23"/>
+      <c r="F94" s="23"/>
+      <c r="G94" s="23"/>
+      <c r="H94" s="23"/>
+    </row>
+    <row r="95" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B95" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C95" s="23"/>
+      <c r="D95" s="23"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="23"/>
+      <c r="G95" s="23"/>
+      <c r="H95" s="23"/>
+    </row>
+    <row r="96" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B96" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
+      <c r="G96" s="23"/>
+      <c r="H96" s="23"/>
+    </row>
+    <row r="97" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B97" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C97" s="23"/>
+      <c r="D97" s="23"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="23"/>
+      <c r="G97" s="23"/>
+      <c r="H97" s="23"/>
+    </row>
+    <row r="98" spans="2:7" ht="53.25" customHeight="1">
+      <c r="B98" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="C98" s="25"/>
+      <c r="D98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="25"/>
+    </row>
+    <row r="101" ht="15">
+      <c r="B101" s="23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="116" ht="15">
+      <c r="B116" s="23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="117" ht="15">
+      <c r="B117" s="23" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B63:H63"/>
-    <mergeCell ref="B64:H64"/>
-    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B98:G98"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B93:I93"/>
+    <mergeCell ref="B94:H94"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
